--- a/sample_runs/2023-11-08/positions.xlsx
+++ b/sample_runs/2023-11-08/positions.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Positions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,8 +51,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,55 +457,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C2" t="n">
-        <v>150</v>
-      </c>
-      <c r="D2" t="n">
-        <v>182</v>
+          <t>CASH</t>
+        </is>
       </c>
       <c r="E2" t="n">
-        <v>18200</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>20</v>
-      </c>
-      <c r="C3" t="n">
-        <v>330</v>
-      </c>
-      <c r="D3" t="n">
-        <v>360</v>
-      </c>
-      <c r="E3" t="n">
-        <v>7200</v>
-      </c>
-      <c r="F3" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CASH</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>86800</v>
+        <v>100000</v>
       </c>
     </row>
   </sheetData>
@@ -597,4 +558,106 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ts</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>citations</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>failure_mode</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>rationale</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2023-11-08T14:15:00+00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Quiet tape; maintain core exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2023-11-08T16:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Macro calendar empty until 2023-11-21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/sample_runs/2023-11-08/positions.xlsx
+++ b/sample_runs/2023-11-08/positions.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,10 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25150</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3" t="n">
+        <v>239.5</v>
+      </c>
+      <c r="D3" t="n">
+        <v>239.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4790</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E4" t="n">
         <v>100000</v>
       </c>
     </row>

--- a/sample_runs/2023-11-08/positions.xlsx
+++ b/sample_runs/2023-11-08/positions.xlsx
@@ -464,7 +464,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>251.5</v>
+        <v>201.2</v>
       </c>
       <c r="D2" t="n">
         <v>251.5</v>
@@ -473,7 +473,7 @@
         <v>25150</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +486,7 @@
         <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>239.5</v>
+        <v>191.6</v>
       </c>
       <c r="D3" t="n">
         <v>239.5</v>
@@ -495,7 +495,7 @@
         <v>4790</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>958</v>
       </c>
     </row>
     <row r="4">
